--- a/services/backend/uploads/datos_escroto.xlsx
+++ b/services/backend/uploads/datos_escroto.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F189"/>
+  <dimension ref="A1:H189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,16 @@
           <t>observ</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>datosclini_limpio</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>sospechadiag_limpio</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -464,15 +474,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>rm escrotal unicamente visualiza pequeño foco hipo t2 1 7 milimetros polo superior testiculo derecho inespecifico relacion microlitiasis correlacionar ecografia</t>
+          <t xml:space="preserve">RM escrotal: Únicamente se visualiza un pequeño foco hipo en T2 de apenas 1,7 milímetros en polo superior del testículo derecho, inespecífico que podría estar en relación con microlitiasis (a correlacionar con ecografía                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>rm escrotal unicamente visualiza pequeño foco hipo t2 17 milimetros polo superior testiculo derecho inespecifico relacion microlitiasis correlacionar ecografia</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -490,15 +510,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dolor TESTICULAR IZQUIERDO 
+NO SE PALPAN MASAS NI MODULACIONES NI HERNIACIONES 
+antecedentes personales  de síntomas similares hace 5 años sin patología tras estudios                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                           </t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DESCARTAR PATOLOGÍA                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>dolor testicular izquierdo no palpan masas ni modulaciones ni herniaciones antecedentes personales sintomas similares 5 años sin patologia estudios</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>descartar patologia</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -516,15 +548,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">testículo izquierdo de menor tamaño y ecoestructura ligeramente heterogénea.
+testículo derecho de tamaño normal, con parénquima de ecoestructura homogénea y de ecogenicidad normal. Persiste lesión hipoecogénica de márgenes imprecisos y con pequeñas calcificaciones groseras, de 7 milímetros, hipervascular
+Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">testículo izquierdo de menor tamaño y ecoestructura ligeramente heterogénea.
+testículo derecho de tamaño normal, con parénquima de ecoestructura homogénea y de ecogenicidad normal. Persiste lesión hipoecogénica de márgenes imprecisos y con pequeñas calcificaciones groseras, de 7 milímetros, hipervascular
+Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>testiculo izquierdo menor tamaño ecoestructura ligeramente heterogenea testiculo derecho tamaño normal parenquima ecoestructura homogenea ecogenicidad normal persiste lesion hipoecogenica margenes imprecisos pequeñas calcificaciones groseras 7 milimetros hipervascular control</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>testiculo izquierdo menor tamaño ecoestructura ligeramente heterogenea testiculo derecho tamaño normal parenquima ecoestructura homogenea ecogenicidad normal persiste lesion hipoecogenica margenes imprecisos pequeñas calcificaciones groseras 7 milimetros hipervascular control</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -542,15 +588,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Quiste hemorrágico en cola de epidídimo derecho                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>quiste hemorragico cola epididimo derecho</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -568,11 +624,21 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nódulo cabeza epidídimo izquierdo, dolorosa ocasionalmente                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>nodulo cabeza epididimo izquierdo dolorosa ocasionalmente</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -590,15 +656,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Varicocele bilateral más en el lado izquierdo
+Quiste epididimo izquierdo
+Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Varicocele bilateral más en el lado izquierdo
+Quiste epididimo izquierdo
+Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>varicocele bilateral izquierdo quiste epididimo izquierdo control</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>varicocele bilateral izquierdo quiste epididimo izquierdo control</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -616,15 +696,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Quiste epididimo derecho                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>quiste epididimo derecho</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -642,15 +732,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bultoma epididimo derecho. Impresiona quiste                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quiste epididimo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>bultoma epididimo derecho impresiona quiste</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>quiste epididimo</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -668,15 +768,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Operado de hidrocele der hace 3 meses
+Test der tumefacto con mínimo hidrocele izquierdo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recidiva
+epididimitis                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                           </t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>operado hidrocele der 3 meses test der tumefacto minimo hidrocele izquierdo</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>recidiva epididimitis</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -694,15 +806,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Aumento de volumen escrotal positivo tras transiluminación                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diagnóstico y decisión de cirugía                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>aumento volumen escrotal positivo transiluminacion</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>diagnostico decision cirugia</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -720,15 +842,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Agrandamiento de hemiescroto izquierdo compatible con varicocele.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Descartar otras lesiones.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>agrandamiento hemiescroto izquierdo compatible varicocele</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>descartar lesiones</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -746,15 +878,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Quistes epididimo derecho                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>quistes epididimo derecho</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -772,15 +914,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Quistes epididimo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">seguimiento                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>quistes epididimo</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>seguimiento</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -798,15 +950,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dolor en testículo derecho, principalmente nutrición enteral epididimo, se aprecia pequeño nódulo, quiste?                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dolor en testículo derecho, principalmente nutrición enteral epididimo, se aprecia pequeño nódulo, quiste?                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>dolor testiculo derecho principalmente nutricion enteral epididimo aprecia pequeño nodulo quiste</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>dolor testiculo derecho principalmente nutricion enteral epididimo aprecia pequeño nodulo quiste</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -824,15 +986,29 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Intervenido de hernia inguinal derecho
+Dolor en testículos bilateralmente
+Exploración dentro de la normalidad                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intervenido de hernia inguinal derecho
+Dolor en testículos bilateralmente
+Exploración dentro de la normalidad                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>intervenido hernia inguinal derecho dolor testiculos bilateralmente exploracion normalidad</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>intervenido hernia inguinal derecho dolor testiculos bilateralmente exploracion normalidad</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -850,15 +1026,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t xml:space="preserve">carcinoma testículo izquierdo hace 15 años                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>carcinoma testiculo izquierdo 15 años</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -876,15 +1062,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dolor inguinal izquierdo, no micción espontanea impresiona de bricolaje significativo ni de hernia inguinal.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                           </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Descartar patología.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>dolor inguinal izquierdo no miccion espontanea impresiona bricolaje significativo ni hernia inguinal</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>descartar patologia</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -902,15 +1098,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t xml:space="preserve">Masa en testículo derecho                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Impresiona quiste de epidídimo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>masa testiculo derecho</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>impresiona quiste epididimo</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -928,15 +1134,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dolor escrotal bilateral de meses de evolución                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>dolor escrotal bilateral meses evolucion</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -954,15 +1170,27 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nódulo con cordón de testículo izquierdo (quiste)
+Molestias en testículo izquierdo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nódulo con cordón de testículo izquierdo (quiste)
+Molestias en testículo izquierdo.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>nodulo cordon testiculo izquierdo quiste molestias testiculo izquierdo</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>nodulo cordon testiculo izquierdo quiste molestias testiculo izquierdo</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -980,15 +1208,26 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Aumento volumen bolsa escrotal izquierdo
+intervenido de hernia inguinal izquierdo recientemente                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hidrocele izquierdo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>aumento volumen bolsa escrotal izquierdo intervenido hernia inguinal izquierdo recientemente</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>hidrocele izquierdo</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1006,15 +1245,27 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Testículo izquierdo aumentado de tamaño
+Quistes epididimo?                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Testículo izquierdo aumentado de tamaño
+Quistes epididimo?                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>testiculo izquierdo aumentado tamaño quistes epididimo</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>testiculo izquierdo aumentado tamaño quistes epididimo</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1032,11 +1283,21 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Control quistes intraarticulares                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>control quistes intraarticulares</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1054,11 +1315,21 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Valoración ECOGRÁFICA DE QUISTE ORDEN DERECHO                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>valoracion ecografica quiste orden derecho</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1076,15 +1347,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Calcificaciones testiculares -                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">seguimiento                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>calcificaciones testiculares</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>seguimiento</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1102,15 +1383,26 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t xml:space="preserve">PRESENTA UN PEQUEÑO BULTO NO ESCROTO ESQUERO
+SOLICITO ECOGRAFÍA TESTICULAR                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BULTO EN ESCROTO ESQUERO                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>presenta pequeño bulto no escroto esquero solicito ecografia testicular</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>bulto escroto esquero</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1128,15 +1420,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Múltiples microlitiasis en el parénquima bilaterales.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>multiples microlitiasis parenquima bilaterales</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1154,15 +1456,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Control de calcificaciones intraarticulares                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control de calcificaciones intraarticulares                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>control calcificaciones intraarticulares</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>control calcificaciones intraarticulares</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1180,15 +1492,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t xml:space="preserve">carcinoma testicular derecho, control testículo contralateral                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
           <t>carcinoma testicular derecho control testiculo contralateral</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1206,15 +1528,26 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Quiste de epididimo bilateral 
+Quiste de inclusión epidérmica (testículo izquierdo)                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                           </t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
           <t>quiste epididimo bilateral quiste inclusion epidermica testiculo izquierdo</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1232,15 +1565,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Neoplasia germinal testicular derecha en seguimiento. Control evolutivo.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neoplasia germinal testicular derecha en seguimiento. Control evolutivo.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
           <t>neoplasia germinal testicular derecha seguimiento control evolutivo</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>neoplasia germinal testicular derecha seguimiento control evolutivo</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1258,11 +1601,21 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Posible hernia inguinal I, con testículo retráctil                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
           <t>hernia inguinal i testiculo retractil</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1280,15 +1633,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t xml:space="preserve">DOLOR ESCROTAL                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESCROTAL                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>dolor escrotal</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>escrotal</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1306,15 +1669,27 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente de 46 años que presenta molestia en escroto izquierdo de varios días de evolución
+exploración: dentro de la normalidad                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paciente de 46 años que presenta molestia en escroto izquierdo de varios días de evolución
+exploración: dentro de la normalidad                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
           <t>paciente 46 años presenta molestia escroto izquierdo evolucion exploracion normalidad</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>paciente 46 años presenta molestia escroto izquierdo evolucion exploracion normalidad</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1332,15 +1707,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Microcalcificación periférica posterior derecha estable (microlitiasis?) así como pequeño microquiste en tercio medio contralateral de apenas. Quiste epididimo.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
           <t>microcalcificacion periferica posterior derecha estable microlitiasis pequeño microquiste tercio contralateral quiste epididimo</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1358,15 +1743,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hidrocele izquierdo?                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hidrocele izquierdo?                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
           <t>hidrocele izquierdo</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>hidrocele izquierdo</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1384,15 +1779,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>actualizacion varicocele paciente c testiculo previo</t>
+          <t xml:space="preserve">Actualización de varicocele en un paciente con C.testículo previo.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Evaluación de testículo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>actualizacion varicocele paciente ctesticulo previo</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
           <t>evaluacion testiculo</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1410,15 +1815,27 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ecografia 2021 realiza exploracion selectiva ambas regiones inguinales region inguinal derecha evidencia cambios postquirurgicos presencia pequeña hernia probablemente contenido graso evidente maniobra valsalva persiste dolor zona inguinal derecho hidrocele derecho tamaño</t>
+          <t xml:space="preserve">En ecografía 2021:Se realiza exploración selectiva de ambas regiones inguinales, en  la región inguinal derecha con evidencia cambios postquirúrgicos y presencia de pequeña hernia, probablemente con contenido graso, que es evidente durante la maniobra de Valsalva.
+Persiste dolor en zona inguinal derecho
+Hidrocele derecho de mayor tamaño?                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Valora si aumento contenido herniario en zona inguinal derecho (dolor)                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ecografia 2021se realiza exploracion selectiva ambas regiones inguinales region inguinal derecha evidencia cambios postquirurgicos presencia pequeña hernia probablemente contenido graso evidente maniobra valsalva persiste dolor zona inguinal derecho hidrocele derecho tamaño</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>valora aumento contenido herniario zona inguinal derecho dolor</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1436,11 +1853,21 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t xml:space="preserve">carcinoma. testicular. Orquiectomía izquierda + colocación de prótesis. Estudio de testículo contralateral (hidrocele que dificulta exploración). Gracias.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
           <t>carcinoma testicular orquiectomia izquierda colocacion protesis estudio testiculo contralateral hidrocele dificulta exploracion gracias</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1458,15 +1885,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dolor testicular izquierdo. de 2 meses de evolución.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
           <t>dolor testicular izquierdo 2 meses evolucion</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1484,15 +1921,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t xml:space="preserve">area nodular paratesticular izquierdo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Descartar t adenoideo?                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
           <t>area nodular paratesticular izquierdo</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>descartar t adenoideo</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1510,15 +1957,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t xml:space="preserve">REVISIÓN CALCIFICACIONES Y DISMINUCIÓN TAMAÑO TESTÍCULO DERECHO                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTROL                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
           <t>revision calcificaciones disminucion tamaño testiculo derecho</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1536,15 +1993,27 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Testículo izquierdo de mayor tamaño ligeramente doloroso
+Refiere que se inflama en ocasiones y mejora con antibióticos                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Testículo izquierdo de mayor tamaño ligeramente doloroso
+Refiere que se inflama en ocasiones y mejora con antibióticos                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
           <t>testiculo izquierdo tamaño ligeramente doloroso refiere inflama ocasiones mejora antibioticos</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>testiculo izquierdo tamaño ligeramente doloroso refiere inflama ocasiones mejora antibioticos</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1562,15 +2031,27 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente psiquiátrico.. esquizofrenia
+Dolor en ambos testículos, testículos en ascensor                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paciente psiquiátrico.. esquizofrenia
+Dolor en ambos testículos, testículos en ascensor                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
           <t>paciente psiquiatrico esquizofrenia dolor testiculos testiculos ascensor</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>paciente psiquiatrico esquizofrenia dolor testiculos testiculos ascensor</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1588,15 +2069,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Aumento volumen escrotal derecho                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hidrocele derecho                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
           <t>aumento volumen escrotal derecho</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>hidrocele derecho</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1614,15 +2105,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lesión en epidídimo de aproximadamente 3 centímetros de diámetro que genera molestias.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control de cara a cirugía.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
           <t>lesion epididimo 3 centimetros diametro genera molestias</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>control cara cirugia</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1640,15 +2141,27 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Intervenido de cirugía de quiste epididimo izquierdo  Septiembre 2023
+Persisten molestias en conducto inguinal izquierdo
+Descartar hernia inguinal                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estudio                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
           <t>intervenido cirugia quiste epididimo izquierdo septiembre 2023 persisten molestias conducto inguinal izquierdo descartar hernia inguinal</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>estudio</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1666,11 +2179,21 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente con atrofia testicular y microlitiasis. Control. Gracias                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
           <t>paciente atrofia testicular microlitiasis control gracias</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1688,15 +2211,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t xml:space="preserve">varon de 77 años con orquitis izquierda y persistencia de inflamación vs hidrocele reactivo. Proteus multiresistente.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comprobar resolución y descartar hidrocele residual. gracias                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
           <t>varon 77 años orquitis izquierda persistencia inflamacion vs hidrocele reactivo proteus multiresistente</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>comprobar resolucion descartar hidrocele residual gracias</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1714,15 +2247,27 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>n dulo testiculo derecho exploracion impresiona pequeño quiste cabeza epididimo</t>
+          <t xml:space="preserve">N´dulo en testículo derecho
+exploración: impresiona de pequeño quiste en cabeza de epididimo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>n dulo testiculo derecho exploracion impresiona pequeño quiste cabeza epididimo</t>
+          <t xml:space="preserve">N´dulo en testículo derecho
+exploración: impresiona de pequeño quiste en cabeza de epididimo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>ndulo testiculo derecho exploracion impresiona pequeño quiste cabeza epididimo</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>ndulo testiculo derecho exploracion impresiona pequeño quiste cabeza epididimo</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1740,15 +2285,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hematoma escrotal, control. Por favor, realizar también ecografía próstata (ver volumen).                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hematoma escrotal.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
           <t>hematoma escrotal control favor ecografia prostata volumen</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>hematoma escrotal</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1766,15 +2321,26 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Disfunción eréctil
+testosterona baja                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valorar estructura y tamaño testicular                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
           <t>disfuncion erectil testosterona baja</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>valorar estructura tamaño testicular</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1792,15 +2358,26 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t xml:space="preserve">VARON DE 30 AÑOS, CON DOLOR TESTICULAR DERECHO DE MESES DE EVOLUCIÓN
+SOLICITO ECOGRAFÍA TESTICULAR BILATERAL                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                           </t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VALORAR AMISTOSOS                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
           <t>varon 30 años dolor testicular derecho meses evolucion solicito ecografia testicular bilateral</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>valorar amistosos</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1818,11 +2395,21 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tumor adenomatoide de epidídimo. Control. Gracias                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
           <t>tumor adenomatoide epididimo control gracias</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1840,15 +2427,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Aumento volumen bolsa escrotal derecho                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hidrocele derecho?                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
           <t>aumento volumen bolsa escrotal derecho</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>hidrocele derecho</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1866,15 +2463,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t xml:space="preserve">HIDROCELE TESTÍCULO DERECHO.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HIDROCELE TESTÍCULO DERECHO.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
           <t>hidrocele testiculo derecho</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>hidrocele testiculo derecho</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1892,15 +2499,27 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t xml:space="preserve">PACIENTE DE 45 AÑOS QUE PRESENTA OCASIONALMENTE DOLOR TESTICULAR IZQUIERDO  QUEMADORA CON antiinflamatorios no esteroideos
+DOLOR COMIENZA EN testículo izquierda Y ASCIENDE
+NO PALPO MASAS                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DESCARTAR PATOLOGÍA TESTICULAR                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
           <t>paciente 45 años presenta ocasionalmente dolor testicular izquierdo quemadora antiinflamatorios no esteroideos dolor comienza testiculo izquierda asciende no palpo masas</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>descartar patologia testicular</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1918,15 +2537,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nódulo para testicular izquierdo (inflamatorio?)                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
           <t>nodulo testicular izquierdo inflamatorio</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1944,15 +2573,26 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t xml:space="preserve">microlitiasis puntiforme en cada testículo
+Quiste epididimo derecho                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
           <t>microlitiasis puntiforme testiculo quiste epididimo derecho</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1970,15 +2610,27 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Absceso escrotal izquierdo que drenó espontáneamente
+Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Absceso escrotal izquierdo que drenó espontáneamente
+Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
           <t>absceso escrotal izquierdo dreno espontaneamente control</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>absceso escrotal izquierdo dreno espontaneamente control</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1996,15 +2648,26 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Epididimitis izquierda sin mejoría a pesar de x3 ciclos de antibiótico                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rogamos valoración escrotal izquierda
+ecuas gracias un saludo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
           <t>epididimitis izquierda sin mejoria x3 ciclos antibiotico</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>rogamos valoracion escrotal izquierda ecuas gracias saludo</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2022,15 +2685,26 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orquiectomía derecho por carcinoma testicular
+Aumento volumen bolsa escrotal izquierdo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hidrocele izquierdo?                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
           <t>orquiectomia derecho carcinoma testicular aumento volumen bolsa escrotal izquierdo</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>hidrocele izquierdo</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2048,15 +2722,32 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente de 81 años quien refiere desde hace unos 5 días dolor testicular izquierdo, sin otros concomitantes.
+Niega fiebre, trastornos urinarios
+Refiere que con los días presenta mejoría.
+Acudió a consulta desde donde refieren,
+EXPLORACIÓN FÍSICA 
+Afebril, hidratado, único.
+Región inguinal: sin aumento de volumen o dolor
+Región genital: testículo derecho de consistencia renitente, se moviliza dentro del escroto, con dolor leve.                                                                                                                                                                                                                                                                                                                                                                                                              </t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Orquidoepididimitis izquierda                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
           <t>paciente 81 años refiere 5 dolor testicular izquierdo sin concomitantes niega fiebre trastornos urinarios refiere presenta mejoria acudio consulta refieren exploracion fisica afebril hidratado unico region inguinal sin aumento volumen dolor region genital testiculo derecho consistencia renitente moviliza escroto dolor leve</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>orquidoepididimitis izquierda</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2074,15 +2765,28 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>varon 27 años paranoide testiculo derecho llama atencion lesion dura 1 5 2cm adherida cara lateral testiculo molesta palpacion sin datos inflamacion ni infeccion</t>
+          <t xml:space="preserve">varon 27 años con paranoide. 
+En Testículo derecho llama la atención lesión dura de 1.5-2cm adherida a cara lateral de testículo, molesta a la palpación, sin datos de inflamación ni infección.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                           </t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Descartar tumor testicular. 
+Analítica con marcadores tumorales pendiente. 
+Muchas gracias                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>varon 27 años paranoide testiculo derecho llama atencion lesion dura 152cm adherida cara lateral testiculo molesta palpacion sin datos inflamacion ni infeccion</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
           <t>descartar tumor testicular analitica marcadores tumorales pendiente gracias</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2100,11 +2804,21 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente con lesión nodular inflamatoria testicular derecha. Control. Gracias.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
           <t>paciente lesion nodular inflamatoria testicular derecha control gracias</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2122,15 +2836,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Varón de 81 años, 2º episodio de trombosis venosa profunda, refiere aumento de tamaño de testículo derecho de unos 6 años de evolución, no doloroso                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                           </t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aumento tamaño testículo derecho de años de evolución                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
           <t>varon 81 años 2º episodio trombosis venosa profunda refiere aumento tamaño testiculo derecho 6 años evolucion no doloroso</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>aumento tamaño testiculo derecho años evolucion</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2148,15 +2872,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hidrocele derecho en evolución sintáctico                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">en espera de cirugía, Control posquirúrgico                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
           <t>hidrocele derecho evolucion sintactico</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>espera cirugia control posquirurgico</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2174,15 +2908,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tumor germinal mixto de testículo izquierdo intervenido. Control evolutivo. NED.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tumor germinal mixto de testículo izquierdo intervenido. Control evolutivo. NED.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
           <t>tumor germinal mixto testiculo izquierdo intervenido control evolutivo ned</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>tumor germinal mixto testiculo izquierdo intervenido control evolutivo ned</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2200,15 +2944,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Aumento de volumen escrotal derecho..                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
           <t>aumento volumen escrotal derecho</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2226,15 +2980,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dolor en cabeza de epidídimo, refiere crecimiento progresivo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
           <t>dolor cabeza epididimo refiere crecimiento progresivo</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2252,15 +3016,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Varicocele izquierdo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
           <t>varicocele izquierdo</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2278,15 +3052,26 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>orquiectomia derecha implante testicular silicona tgns control testicular contralateral</t>
+          <t xml:space="preserve">orquiectomía derecha-implante testicular silicona por TGNS
+Control testicular contralateral                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Control testicular IZQUIERDO                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>orquiectomia derechaimplante testicular silicona tgns control testicular contralateral</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
           <t>control testicular izquierdo</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2304,15 +3089,27 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Prostatismo
+infección del tracto urinario de repetición
+Orquioepididimitis izquierdo con buena evolución con tratamiento pero aún persiste engrosamiento en epididimo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
           <t>prostatismo infeccion tracto urinario repeticion orquioepididimitis izquierdo evolucion tratamiento persiste engrosamiento epididimo</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2330,15 +3127,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t xml:space="preserve">QUISTE EPIDIDIMO IZQUIERDO, ÚLTIMO CONTROL CRERCIMEITNO                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
           <t>quiste epididimo izquierdo control crercimeitno</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2356,15 +3163,26 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Microcalcificaciones testiculares bilaterales
+Quiste epididimo izquierdo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
           <t>microcalcificaciones testiculares bilaterales quiste epididimo izquierdo</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2382,15 +3200,26 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Varicocele izquierdo intervenido
+Refiere dolor en testículo derecho que se irradia zona  inguinal                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Varicocele derecho?                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
           <t>varicocele izquierdo intervenido refiere dolor testiculo derecho irradia zona inguinal</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>varicocele derecho</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2408,15 +3237,27 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Prostatectomía radical 2021 (carcinoma próstata)
+ Dolor al tocar el epididimo bilateralmente                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prostatectomía radical 2021 (carcinoma próstata)
+ Dolor al tocar el epididimo bilateralmente                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                           </t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
           <t>prostatectomia radical 2021 carcinoma prostata dolor tocar epididimo bilateralmente</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>prostatectomia radical 2021 carcinoma prostata dolor tocar epididimo bilateralmente</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2434,11 +3275,21 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente con atrofia testicular izquierda tras arteria coronaria circunfleja de hernia inguinal. Control. Gracias.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
           <t>paciente atrofia testicular izquierda arteria coronaria circunfleja hernia inguinal control gracias</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2456,15 +3307,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Xesticulo derecho de menor tamaño con epidémico aumentado de tamaño, engrosado e irregular                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
           <t>xesticulo derecho menor tamaño epidemico aumentado tamaño engrosado irregular</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2482,15 +3343,26 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Molestias testiculares
+ ANGIOQUERATOMAS DEL ESCROTO.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Descartar varicocele                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
           <t>molestias testiculares angioqueratomas escroto</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>descartar varicocele</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2508,15 +3380,27 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Refiere molestias en testículos de forma intermitente, que alivian con AINE
+Vasectomía hace unos 20 años                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Refiere molestias en testículos de forma intermitente, que alivian con AINE
+Vasectomía hace unos 20 años                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
           <t>refiere molestias testiculos forma intermitente alivian aine vasectomia 20 años</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>refiere molestias testiculos forma intermitente alivian aine vasectomia 20 años</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2534,11 +3418,21 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente con sospecha de quiste de epidídimo izquierdo. Gracias                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
           <t>paciente sospecha quiste epididimo izquierdo gracias</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2556,15 +3450,26 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Varón de 54 años, inflamación de testículos desde hace 6 meses.
+A la exploración, indurados                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solicito ecografía testicular                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
           <t>varon 54 años inflamacion testiculos 6 meses exploracion indurados</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>solicito ecografia testicular</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2582,11 +3487,21 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dolor testículo izquierdo. Descartar complicación                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
           <t>dolor testiculo izquierdo descartar complicacion</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2604,15 +3519,26 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dolor testículo izquierdo
+exploración: dentro de la normalidad                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">varicocele?                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
           <t>dolor testiculo izquierdo exploracion normalidad</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>varicocele</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2630,15 +3556,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tumor de Células Germinales No Seminomadismos mixto (teratoma con carcinoma embrionario) de testículo derecho pT2 (invasión de epidídimo) N0 M0, S0, Estadio IB, sin factores de riesgo (no invasión linfovascular ni del cordón espermático ni de escroto) en Julio 2019 + BE x 1 ciclo que recibió en septiembre de 2019.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control en seguimiento                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
           <t>tumor celulas germinales no seminomadismos mixto teratoma carcinoma embrionario testiculo derecho pt2 invasion epididimo n0 m0 s0 estadio ib sin factores riesgo no invasion linfovascular ni cordon espermatico ni escroto julio 2019 be x 1 ciclo recibio septiembre 2019</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>control seguimiento</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2656,15 +3592,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
+          <t xml:space="preserve">BULT9OMA TESTICULAR                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BULTOMA                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
           <t>bult9oma testicular</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>bultoma</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2682,15 +3628,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
+          <t xml:space="preserve">DOLOR ESCROTAL                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DOLOR ESCROTAL                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
           <t>dolor escrotal</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>dolor escrotal</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2708,15 +3664,27 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
+          <t xml:space="preserve">Prostatectomía por carcinoma +radioterapia
+Dolor testículo derecho, engrosamiento epididimo derecho
+.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Epididimitis derecho?                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
           <t>prostatectomia carcinoma radioterapia dolor testiculo derecho engrosamiento epididimo derecho</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>epididimitis derecho</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2734,15 +3702,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t xml:space="preserve">Calcificación 1 milímetros en epidídimo izquierdo, seguimiento                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seguimiento evolutivo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                           </t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
           <t>calcificacion 1 milimetros epididimo izquierdo seguimiento</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>seguimiento evolutivo</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2760,15 +3738,29 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente intervenido de criptorquidia derecha en la infancia
+Actualmente testículo ascendido que se consigue descender parcialmente desde el canal inguinal hacia el escroto.
+Impresiona de normal                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paciente intervenido de criptorquidia derecha en la infancia
+Actualmente testículo ascendido que se consigue descender parcialmente desde el canal inguinal hacia el escroto.
+Impresiona de normal                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
           <t>paciente intervenido criptorquidia derecha infancia actualmente testiculo ascendido descender parcialmente canal inguinal escroto impresiona normal</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>paciente intervenido criptorquidia derecha infancia actualmente testiculo ascendido descender parcialmente canal inguinal escroto impresiona normal</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2786,15 +3778,27 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t xml:space="preserve">Infertilidad
+Quistes epididimo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Infertilidad
+Quistes epididimo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
           <t>infertilidad quistes epididimo</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>infertilidad quistes epididimo</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2812,15 +3816,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Aumento de tamaño testicular. Posible hidrocele a tensión.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirmar hidrocele.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
           <t>aumento tamaño testicular hidrocele tension</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>confirmar hidrocele</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2838,15 +3852,26 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
+          <t xml:space="preserve">Aumento volumen escrotal derecho
+Doloroso                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDF valorar intervención                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
           <t>aumento volumen escrotal derecho doloroso</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>pdf valorar intervencion</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2864,15 +3889,26 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bulto en testículo izquierdo que no le dio importancia, pero ahora le molesta y cree le aumento de tamaño.
+exploración: no palpo claro nódulo o bultoma                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nódulo testículo izquierdo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
           <t>bulto testiculo izquierdo no importancia molesta cree aumento tamaño exploracion no palpo nodulo bultoma</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>nodulo testiculo izquierdo</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2890,15 +3926,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dolor en región inguinal derecha.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hernia inguinal derecha.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
           <t>dolor region inguinal derecha</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>hernia inguinal derecha</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2916,15 +3962,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orquiepididimitis derecha.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control posterior tratamiento.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
           <t>orquiepididimitis derecha</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>control posterior tratamiento</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2942,15 +3998,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dolor testicular bilateral                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
           <t>dolor testicular bilateral</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2968,15 +4034,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
+          <t xml:space="preserve">exploración: aumento volumen bolsa escrotal derecho                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hidrocele derecho?                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
           <t>exploracion aumento volumen bolsa escrotal derecho</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>hidrocele derecho</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2994,15 +4070,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
+          <t xml:space="preserve">Pequeño nódulo en testículo derecho, no doloroso                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pequeño nódulo en testículo derecho, no doloroso                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
           <t>pequeño nodulo testiculo derecho no doloroso</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>pequeño nodulo testiculo derecho no doloroso</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3020,15 +4106,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
+          <t xml:space="preserve">Aumento del volumen escrotal izquierdo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Impresiona de hidrocele izquierdo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
           <t>aumento volumen escrotal izquierdo</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="H102" t="inlineStr">
         <is>
           <t>impresiona hidrocele izquierdo</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3046,15 +4142,27 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Posible hidrocele derecho
+**paciente refiere testículo indurado. a la exploración impresiona de hidrocele                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Descartar complicación hidrocele
+muchas gracias un saludo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
           <t>hidrocele derecho paciente refiere testiculo indurado exploracion impresiona hidrocele</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="H103" t="inlineStr">
         <is>
           <t>descartar complicacion hidrocele gracias saludo</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3072,11 +4180,21 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente con orquitis izquierda. Control. Gracias                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
           <t>paciente orquitis izquierda control gracias</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3094,15 +4212,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
+          <t xml:space="preserve">microlitiasis bilaterales  testiculares                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
           <t>microlitiasis bilaterales testiculares</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="H105" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3120,15 +4248,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sospecha de varicocele. En lista de espera para cirugía.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Descartar otros procesos.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
           <t>sospecha varicocele lista espera cirugia</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="H106" t="inlineStr">
         <is>
           <t>descartar procesos</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3146,15 +4284,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente intervenido de hernia inguinal izquierdo. Hematoma organizado en cordón espermático. Hidrocele izquierdo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
           <t>paciente intervenido hernia inguinal izquierdo hematoma organizado cordon espermatico hidrocele izquierdo</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="H107" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3172,15 +4320,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
+          <t xml:space="preserve">DOLOR TESTICULAR                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DOLOR TESTICULAR                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
           <t>dolor testicular</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="H108" t="inlineStr">
         <is>
           <t>dolor testicular</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3198,15 +4356,26 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
+          <t xml:space="preserve">ORQUIOEPIDIDIMITIS DERECHA                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DESCARTAR COMPLICACIÓN/CRONICIDAD
+MUCHAS GRACIAS, UN SALUDO                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
           <t>orquioepididimitis derecha</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>descartar complicacion cronicidad gracias saludo</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>descartar complicacioncronicidad gracias saludo</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3224,15 +4393,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nódulo es testículo derecho                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nódulo es testículo derecho                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
           <t>nodulo testiculo derecho</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="H110" t="inlineStr">
         <is>
           <t>nodulo testiculo derecho</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3250,11 +4429,21 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
+          <t xml:space="preserve">QUISTES BILATERALES, CONTROL (CREE QUE LE CRECIERON)                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
           <t>quistes bilaterales control cree crecieron</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3272,15 +4461,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hidrocele izquierdo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hidrocele izquierdo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
           <t>hidrocele izquierdo</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="H112" t="inlineStr">
         <is>
           <t>hidrocele izquierdo</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3298,15 +4497,31 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente de 17 años, quien refiere dolor testicular izquierdo desde hace 2 días, por lo cual acudió por urgencias e indicaron tratamiento con paracetamol y fue valorado por Urología.
+Refiere persistencia del dolor y hoy inicia dolor abdominal cólico en hemiabdomen inferior con 3 evacuaciones líquidas sin moco ni sangre.
+Niega fiebre, alteraciones urinarias, náuseas.
+EXPLORACIÓN FÍSICA 
+Afebril, hidratado, único.
+Abdomen: blando, depresible, doloroso leve en hipogastrio y ambas fosas iliacas sin signos de irritación peritoneal.
+Genitales: testículos simétricos, dolor leve en el izquierdo el cual se encuentra de consistencia renitente y móvil en bolsa escrotal.                                                                                                                                                                </t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dolor testicular bilateral                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
           <t>paciente 17 años refiere dolor testicular izquierdo 2 acudio urgencias indicaron tratamiento paracetamol valorado urologia refiere persistencia dolor inicia dolor abdominal colico hemiabdomen inferior 3 evacuaciones liquidas sin moco ni sangre niega fiebre alteraciones urinarias nauseas exploracion fisica afebril hidratado unico abdomen blando depresible doloroso leve hipogastrio ambas fosas iliacas sin signos irritacion peritoneal genitales testiculos simetricos dolor leve izquierdo consistencia renitente movil bolsa escrotal</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="H113" t="inlineStr">
         <is>
           <t>dolor testicular bilateral</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3324,11 +4539,21 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dolor y bultoma testículo I                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
           <t>dolor bultoma testiculo i</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3346,15 +4571,27 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
+          <t xml:space="preserve">testículo ATRÓFICO CRÓNICO                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RUEGO ecografía
+MUCHAS GRACIAS
+UN SALUDO                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
           <t>testiculo atrofico cronico</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="H115" t="inlineStr">
         <is>
           <t>ruego ecografia gracias saludo</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3372,15 +4609,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
+          <t xml:space="preserve">Varón de 73 años con induración a nivel de testículo izquierdo (no hidrocele)                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Descartar lesión                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
           <t>varon 73 años induracion nivel testiculo izquierdo no hidrocele</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="H116" t="inlineStr">
         <is>
           <t>descartar lesion</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3398,15 +4645,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
+          <t xml:space="preserve">ecografía escrotal Mayo2024: Se evidencia moderada cuantía de hidrocele izquierdo con pequeñas imágenes ecogénicas que se movilizan durante el estudio, puntiformes, probablemente en relación con detritus. El epidídimo izquierdo presenta un tamaño dentro de la normalidad, evidenciando un parénquima heterogéneo. Hallazgos que pueden estar en relación con secuelas de patología inflamatoria remota.                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
           <t>ecografia escrotal mayo2024 evidencia moderada cuantia hidrocele izquierdo pequeñas imagenes ecogenicas movilizan estudio puntiformes probablemente relacion detritus epididimo izquierdo presenta tamaño normalidad evidenciando parenquima heterogeneo hallazgos relacion secuelas patologia inflamatoria remota</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="H117" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3424,15 +4681,26 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orquidopexia derecha en noviembre de 2022
+Pequeño Varicocele izquierdo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
           <t>orquidopexia derecha noviembre 2022 pequeño varicocele izquierdo</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="H118" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3450,11 +4718,21 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
+          <t xml:space="preserve">Quiste cordón testículo derecho; control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
           <t>quiste cordon testiculo derecho control</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3472,15 +4750,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente de 14 años con varicocele izquierdo. En la exploración, palpable con dificultad. Asintomático. Ruego valoración de tamaño testicular. Gracias                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Varicocele izquierdo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
           <t>paciente 14 años varicocele izquierdo exploracion palpable dificultad asintomatico ruego valoracion tamaño testicular gracias</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="H120" t="inlineStr">
         <is>
           <t>varicocele izquierdo</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3498,11 +4786,21 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente con quistes de epidídimo bilaterales, molestias escrotales y sospecha de epididimitis. Control. Gracias                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
           <t>paciente quistes epididimo bilaterales molestias escrotales sospecha epididimitis control gracias</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3520,15 +4818,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente de 14 años con quiste de epidídimo derecho. Ruego control.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quiste de epidídimo derecho                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
           <t>paciente 14 años quiste epididimo derecho ruego control</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="H122" t="inlineStr">
         <is>
           <t>quiste epididimo derecho</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3546,15 +4854,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente de 14 años con varicocele izquierdo grado I. Asintomático. Ruego valoración de tamaño testicular. Gracias                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Varicocele izquierdo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
           <t>paciente 14 años varicocele izquierdo grado i asintomatico ruego valoracion tamaño testicular gracias</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="H123" t="inlineStr">
         <is>
           <t>varicocele izquierdo</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3572,15 +4890,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
+          <t xml:space="preserve">DOLOR TESTICULAR 16 AÑOS                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DOLOR TESTICULAR                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
           <t>dolor testicular 16 años</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="H124" t="inlineStr">
         <is>
           <t>dolor testicular</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3598,15 +4926,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
+          <t xml:space="preserve">DOLOR TESTICULAR 16 AÑOS                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DOLOR TESTICULAR                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
           <t>dolor testicular 16 años</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="H125" t="inlineStr">
         <is>
           <t>dolor testicular</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3624,15 +4962,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>14 ños varicocele izquierdo grado ii solicita ecografia control tamaño testicular</t>
+          <t xml:space="preserve">14 a´ños, varicocele izquierdo grado II, se solicita ecografía de control para tamaño testicular                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
+          <t xml:space="preserve">Varicocele izquierdo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>14 años varicocele izquierdo grado ii solicita ecografia control tamaño testicular</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
           <t>varicocele izquierdo</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3650,15 +4998,26 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente de 13 años intervenido de criptorquidia derecha. Asimetría testicular. Quiste de epidídimo izquierdo. Ruego valoración. Gracias                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quiste de epidídimo izquierdo
+Asimetría testicular                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
           <t>paciente 13 años intervenido criptorquidia derecha asimetria testicular quiste epididimo izquierdo ruego valoracion gracias</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="H127" t="inlineStr">
         <is>
           <t>quiste epididimo izquierdo asimetria testicular</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3676,15 +5035,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente con quiste de epidídimo izquierdo y orquitis tratada. Control gracias.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quiste epidídimo. control tras orquitis                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
           <t>paciente quiste epididimo izquierdo orquitis tratada control gracias</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="H128" t="inlineStr">
         <is>
           <t>quiste epididimo control orquitis</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3702,15 +5071,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
+          <t xml:space="preserve">Varón de 13 años con varicocele izquierdo. Asintomático. Visible en bipedestación. Ruego valoración de tamaño testicular izquierdo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Varicocele izquierdo. Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
           <t>varon 13 años varicocele izquierdo asintomatico visible bipedestacion ruego valoracion tamaño testicular izquierdo</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="H129" t="inlineStr">
         <is>
           <t>varicocele izquierdo control</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3728,15 +5107,26 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
+          <t xml:space="preserve">Seminoma estadio IB en revisiones. En testículo derecho se palpa bultoma a nivel de epidídimo sugestivo de espermatocele.
+Control.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ecografía escroto.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
           <t>seminoma estadio ib revisiones testiculo derecho palpa bultoma nivel epididimo sugestivo espermatocele control</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="H130" t="inlineStr">
         <is>
           <t>ecografia escroto</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3754,11 +5144,21 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
+          <t xml:space="preserve">Evolución hematoma testículo izquierdo PO                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
           <t>evolucion hematoma testiculo izquierdo po</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3776,15 +5176,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente de 11 años con varicocele izquierdo. Asintomático. Ruego valoración de tamaño testicular. Gracias                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Varicocele izquierdo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
           <t>paciente 11 años varicocele izquierdo asintomatico ruego valoracion tamaño testicular gracias</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="H132" t="inlineStr">
         <is>
           <t>varicocele izquierdo</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3802,15 +5212,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
+          <t xml:space="preserve">Varón de 41 años con dolor en base escrotal intenso de 1 año de evolución. Realizadas múltiples pruebas que descartan patología. Exploración perianal sin hallazgos, descartado origen anorrectal. En ecografía previa, se visualiza varicocele y posible tromboflebitis.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control. Descartar otras lesiones                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
           <t>varon 41 años dolor base escrotal intenso 1 año evolucion realizadas multiples pruebas descartan patologia exploracion perianal sin hallazgos descartado origen anorrectal ecografia previa visualiza varicocele tromboflebitis</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
+      <c r="H133" t="inlineStr">
         <is>
           <t>control descartar lesiones</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3828,15 +5248,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
+          <t xml:space="preserve">Microlitiasis aislada en testículo derecho (al menos 2. Sin claras lesiones focales sólidas intraarticulares.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
           <t>microlitiasis aislada testiculo derecho 2 sin claras lesiones focales solidas intraarticulares</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
+      <c r="H134" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3854,15 +5284,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente de 14 años con varicocele izquierdo. Ruego valoración y medición del tamaño testicular  cm3. Gracias                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                           </t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Varicocele izquierdo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
           <t>paciente 14 años varicocele izquierdo ruego valoracion medicion tamaño testicular cm3 gracias</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
+      <c r="H135" t="inlineStr">
         <is>
           <t>varicocele izquierdo</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3880,15 +5320,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
+          <t xml:space="preserve">Aumento tamaño escrotal. gracias.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aumento tamaño escrotal. gracias.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
           <t>aumento tamaño escrotal gracias</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
+      <c r="H136" t="inlineStr">
         <is>
           <t>aumento tamaño escrotal gracias</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3906,11 +5356,21 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
+          <t xml:space="preserve">Control testículo único por carcinoma mestastásico                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
           <t>control testiculo unico carcinoma mestastasico</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3928,15 +5388,27 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dolor testicular bilateral
+exploración: dentro de la normalidad                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dolor testicular bilateral
+exploración: dentro de la normalidad                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
           <t>dolor testicular bilateral exploracion normalidad</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="H138" t="inlineStr">
         <is>
           <t>dolor testicular bilateral exploracion normalidad</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3954,15 +5426,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
+          <t xml:space="preserve">Microlitiasis testiculares y quiste de epididimo.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control evolutivo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
           <t>microlitiasis testiculares quiste epididimo</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="H139" t="inlineStr">
         <is>
           <t>control evolutivo</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3980,15 +5462,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
+          <t xml:space="preserve">BULTOMA TESTICULAR                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BULTOMA TESTICULAR                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
           <t>bultoma testicular</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
+      <c r="H140" t="inlineStr">
         <is>
           <t>bultoma testicular</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4006,15 +5498,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hipogonadismo primario. Estudio infertilidad.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                           </t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hipogonadismo primario.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
           <t>hipogonadismo primario estudio infertilidad</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="H141" t="inlineStr">
         <is>
           <t>hipogonadismo primario</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4032,15 +5534,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
+          <t xml:space="preserve">Varón de 16 años que nota bultoma en hemiescroto izquierdo doloroso. Exploración: normal                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Descartar lesión                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
           <t>varon 16 años nota bultoma hemiescroto izquierdo doloroso exploracion normal</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="H142" t="inlineStr">
         <is>
           <t>descartar lesion</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4058,15 +5570,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
+          <t xml:space="preserve">TUMORACIÓN ESCROTAL                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TUMORACIÓN ESCROTAL                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
           <t>tumoracion escrotal</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
+      <c r="H143" t="inlineStr">
         <is>
           <t>tumoracion escrotal</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4084,15 +5606,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente de 5 años con sospecha de torsión testículo izquierdo neonatal. testículo derecho en bolsa. No palpo restos izquierdos. Ruego valoración. Gracias                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monarquía derecha por torsión testicular izquierda neonatal                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
           <t>paciente 5 años sospecha torsion testiculo izquierdo neonatal testiculo derecho bolsa no palpo restos izquierdos ruego valoracion gracias</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
+      <c r="H144" t="inlineStr">
         <is>
           <t>monarquia derecha torsion testicular izquierda neonatal</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4110,11 +5642,21 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente con molestias testiculares izquierdas, mínimo hidrocele. Exploración ok. Gracias.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
           <t>paciente molestias testiculares izquierdas minimo hidrocele exploracion ok gracias</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4132,15 +5674,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
+          <t xml:space="preserve">Control de microcalcificaciones. gracias.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control de microcalcificaciones. gracias.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
           <t>control microcalcificaciones gracias</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
+      <c r="H146" t="inlineStr">
         <is>
           <t>control microcalcificaciones gracias</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4158,15 +5710,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente de dos años con quiste de epidídimo izquierdo. Ruego control evolutivo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quiste de epidídimo izquierdo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
           <t>paciente años quiste epididimo izquierdo ruego control evolutivo</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
+      <c r="H147" t="inlineStr">
         <is>
           <t>quiste epididimo izquierdo</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4184,15 +5746,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
+          <t xml:space="preserve">DOLOR ESCROTAL                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DOLOR                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                           </t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
           <t>dolor escrotal</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
+      <c r="H148" t="inlineStr">
         <is>
           <t>dolor</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4210,15 +5782,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
+          <t xml:space="preserve">VARICOCELE                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VARICOCELE                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
           <t>varicocele</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
+      <c r="H149" t="inlineStr">
         <is>
           <t>varicocele</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4236,15 +5818,27 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
+          <t xml:space="preserve">Testículo derecho que asciende por canal inguinal desde hace unos 2 meses, doloroso
+Nódulo en cabeza del epididimo (quiste?)                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Testículo derecho que asciende por canal inguinal desde hace unos 2 meses, doloroso
+Nódulo en cabeza del epididimo (quiste?)                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
           <t>testiculo derecho asciende canal inguinal 2 meses doloroso nodulo cabeza epididimo quiste</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
+      <c r="H150" t="inlineStr">
         <is>
           <t>testiculo derecho asciende canal inguinal 2 meses doloroso nodulo cabeza epididimo quiste</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4262,15 +5856,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente con varicocele en testículo izquierdo, sintáctico                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control evolutivo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
           <t>paciente varicocele testiculo izquierdo sintactico</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
+      <c r="H151" t="inlineStr">
         <is>
           <t>control evolutivo</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4288,15 +5892,26 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente de 77 años con aumento de tamaño de testículo derecho de reciente aparición; a la palpación se aprecia zona indurada en región posterior. No datos de infección en analítica.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Descartar malignidad.
+Gracias.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
           <t>paciente 77 años aumento tamaño testiculo derecho reciente aparicion palpacion aprecia zona indurada region posterior no datos infeccion analitica</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
+      <c r="H152" t="inlineStr">
         <is>
           <t>descartar malignidad gracias</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4314,15 +5929,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
+          <t xml:space="preserve">exploración: aumento volumen bolsa escrotal izquierdo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exploración: aumento volumen bolsa escrotal izquierdo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
           <t>exploracion aumento volumen bolsa escrotal izquierdo</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
+      <c r="H153" t="inlineStr">
         <is>
           <t>exploracion aumento volumen bolsa escrotal izquierdo</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4340,15 +5965,26 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
+          <t xml:space="preserve">GRAN HERNIA PINGÜINO ESCROTAL
+HIDROCELE DUCO                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDF valorar cirugía                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
           <t>hernia pingüino escrotal hidrocele duco</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
+      <c r="H154" t="inlineStr">
         <is>
           <t>pdf valorar cirugia</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4366,15 +6002,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dolor testicular izquierdo en relación a Orquitis puesto en contexto de enucleación prostática.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control..                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
           <t>dolor testicular izquierdo relacion orquitis puesto contexto enucleacion prostatica</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
+      <c r="H155" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4392,15 +6038,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
+          <t xml:space="preserve">Infertilidad primaria                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lo llamaron para ecografía y estaba fuera. no se la reprogramaron                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
           <t>infertilidad primaria</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
+      <c r="H156" t="inlineStr">
         <is>
           <t>llamaron ecografia no reprogramaron</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4418,15 +6074,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>valoracion calcificaciones testiculo derecho graica s</t>
+          <t xml:space="preserve">VALORACIÓN DE CALCIFICACIONES EN testículo DERECHO. GRAICA.S                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>valoracion calcificaciones testiculo derecho graica s</t>
+          <t xml:space="preserve">VALORACIÓN DE CALCIFICACIONES EN testículo DERECHO. GRAICA.S                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>valoracion calcificaciones testiculo derecho graicas</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>valoracion calcificaciones testiculo derecho graicas</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4444,15 +6110,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente que refiere desde hace 1 año dolor testicular derecho, con discreta aumento de volumen                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dolor en epidídimo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
           <t>paciente refiere 1 año dolor testicular derecho discreta aumento volumen</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
+      <c r="H158" t="inlineStr">
         <is>
           <t>dolor epididimo</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4470,15 +6146,26 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
+          <t xml:space="preserve">Control en Colombia de varicocele izquierdo y calcificaciones testiculares
+Dolor leve abdominal en lado izquierdo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Varicocele izquierdo?                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
           <t>control colombia varicocele izquierdo calcificaciones testiculares dolor leve abdominal izquierdo</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
+      <c r="H159" t="inlineStr">
         <is>
           <t>varicocele izquierdo</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4496,15 +6183,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
+          <t xml:space="preserve">Nódulo en cola de epididimo testículo derecho  (quiste)                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nódulo en cola de epididimo testículo derecho (quiste)                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
           <t>nodulo cola epididimo testiculo derecho quiste</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
+      <c r="H160" t="inlineStr">
         <is>
           <t>nodulo cola epididimo testiculo derecho quiste</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4522,15 +6219,27 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente de 33 años que refiere diagnóstico de varicocele bilateral en Venezuela, pendiente de valorar cirugía
+Dolor escrotal, más en el lado derecho                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paciente de 33 años que refiere diagnóstico de varicocele bilateral en Venezuela, pendiente de valorar cirugía
+Dolor escrotal, más en el lado derecho                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
           <t>paciente 33 años refiere diagnostico varicocele bilateral venezuela pendiente valorar cirugia dolor escrotal derecho</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
+      <c r="H161" t="inlineStr">
         <is>
           <t>paciente 33 años refiere diagnostico varicocele bilateral venezuela pendiente valorar cirugia dolor escrotal derecho</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4548,15 +6257,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>dolor pestes bilateral ex fisica sin hallazgos</t>
+          <t xml:space="preserve">Dolor pestes bilateral-ex física sin hallazgos                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
+          <t xml:space="preserve">control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>dolor pestes bilateralex fisica sin hallazgos</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4574,15 +6293,26 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente de 35 años con inflamación de testículo derecho e induración de cabeza de epididimo derecha.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Descartar quiste/masas/resolución cuadro inflamatorio.
+Gracias.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
           <t>paciente 35 años inflamacion testiculo derecho induracion cabeza epididimo derecha</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>descartar quiste masas resolucion cuadro inflamatorio gracias</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr"/>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>descartar quistemasasresolucion cuadro inflamatorio gracias</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4600,15 +6330,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bultoma y dolor en bolsa escrotal izquierdo que no impresiona relacionado con el testículo en su polo inferior                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bultoma y dolor en bolsa escrotal izquierdo que no impresiona relacionado con el testículo en su polo inferior                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
           <t>bultoma dolor bolsa escrotal izquierdo no impresiona relacionado testiculo polo inferior</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
+      <c r="H164" t="inlineStr">
         <is>
           <t>bultoma dolor bolsa escrotal izquierdo no impresiona relacionado testiculo polo inferior</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4626,15 +6366,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
+          <t xml:space="preserve">BULTOMA TESTICULAR                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BULTOMA ESCROTAL                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
           <t>bultoma testicular</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
+      <c r="H165" t="inlineStr">
         <is>
           <t>bultoma escrotal</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4652,11 +6402,21 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
+          <t xml:space="preserve">Induración testículo  izquierdo tras antibióticos 1 mes (Varios ciclos)                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
           <t>induracion testiculo izquierdo antibioticos 1 mes ciclos</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4674,15 +6434,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente con microlitiasis testiculares, varicocele bilateral y dudosa hernia derecha. Control.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control microlitiasis, varicocele y hernia.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
           <t>paciente microlitiasis testiculares varicocele bilateral dudosa hernia derecha control</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
+      <c r="H167" t="inlineStr">
         <is>
           <t>control microlitiasis varicocele hernia</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4700,11 +6470,21 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente con pestes en ascensor, molestias inguinoescrotales de repetición, dificultad para exploración testicular. Control. Gracias.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
           <t>paciente pestes ascensor molestias inguinoescrotales repeticion dificultad exploracion testicular control gracias</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4722,11 +6502,21 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente interveniente de quiste de epidídimo izquierdo. Ahora aumento de volumen testículo e induración. Control. Gracias,                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
           <t>paciente interveniente quiste epididimo izquierdo aumento volumen testiculo induracion control gracias</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -4744,11 +6534,21 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente con orquiepididimitis tras vasectomía, aumento de volumen escrotal derecho, tumefacción y dolor. Control. Gracias.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
           <t>paciente orquiepididimitis vasectomia aumento volumen escrotal derecho tumefaccion dolor control gracias</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -4766,11 +6566,21 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
+          <t xml:space="preserve">Paciente con quiste de epidídimo izquierdo. Control. Gracias                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
           <t>paciente quiste epididimo izquierdo control gracias</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -4788,15 +6598,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
+          <t xml:space="preserve">Quiste epididimo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
           <t>quiste epididimo</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
+      <c r="H172" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -4814,15 +6634,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
+          <t xml:space="preserve">BULTOMA TESTICULAR                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BULTOMA TESTICULAR                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
           <t>bultoma testicular</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
+      <c r="H173" t="inlineStr">
         <is>
           <t>bultoma testicular</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4840,15 +6670,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
+          <t xml:space="preserve">QUISTE EPIDIDIMO                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUISTE                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                          </t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
           <t>quiste epididimo</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
+      <c r="H174" t="inlineStr">
         <is>
           <t>quiste</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4866,11 +6706,21 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
+          <t xml:space="preserve">Aumento volumen testículo izquierdo; hidrocele ¿?                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                           </t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
           <t>aumento volumen testiculo izquierdo hidrocele</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -4888,11 +6738,21 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
+          <t xml:space="preserve">Molestias en testículo izquierdo; descartar complicaciones                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
           <t>molestias testiculo izquierdo descartar complicaciones</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -4910,15 +6770,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
+          <t xml:space="preserve">ORQUITIS                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                </t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ORQUITIS                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
           <t>orquitis</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
+      <c r="H177" t="inlineStr">
         <is>
           <t>orquitis</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -4936,15 +6806,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
+          <t xml:space="preserve">QUISTE/ HIDROCELE                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QUITE /HIDROCELE                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
           <t>quiste hidrocele</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
+      <c r="H178" t="inlineStr">
         <is>
           <t>quite hidrocele</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -4962,15 +6842,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
+          <t xml:space="preserve">Testículo der doloroso y endurecido en polo supositorio con quiste de cordón                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Descartar neoplasia                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                   </t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
           <t>testiculo der doloroso endurecido polo supositorio quiste cordon</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
+      <c r="H179" t="inlineStr">
         <is>
           <t>descartar neoplasia</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -4988,17 +6878,27 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
+          <t xml:space="preserve">Valoración por infertilidad. gracias                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valoración por infertilidad. gracias                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                            </t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CITA 09/09: MULTIPLES LLAMADAS DESDE UCCT, ILOCALIZABLE               </t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
           <t>valoracion infertilidad gracias</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
+      <c r="H180" t="inlineStr">
         <is>
           <t>valoracion infertilidad gracias</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CITA 09/09: MULTIPLES LLAMADAS DESDE UCCT, ILOCALIZABLE               </t>
         </is>
       </c>
     </row>
@@ -5018,17 +6918,28 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
+          <t xml:space="preserve">68 Años
+carcinoma próstata bajo riesgo, tratamiento RT en 2014, enfermedad de  Peyronie, en seguimiento por Urología. En último control en enero solicitan ecografía de escroto de control, pero no consta en buzón ni han llamado, por lo que solicito de nuevo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                      </t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">carcinoma próstata bajo riesgo, tratamiento RT en 2014, enfermedad de Peyronie                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CITA 14/09:NO PUEDE/CITA 18/09:NO PUEDE/CITAR A PARTIR 3/10/24        </t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
           <t>68 años carcinoma prostata riesgo tratamiento rt 2014 enfermedad peyronie seguimiento urologia control enero solicitan ecografia escroto control no consta buzon ni llamado solicito</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
+      <c r="H181" t="inlineStr">
         <is>
           <t>carcinoma prostata riesgo tratamiento rt 2014 enfermedad peyronie</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CITA 14/09:NO PUEDE/CITA 18/09:NO PUEDE/CITAR A PARTIR 3/10/24        </t>
         </is>
       </c>
     </row>
@@ -5048,15 +6959,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
+          <t xml:space="preserve">Control en paciente con molestias testiculares persistentes y oligospermia                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CITA 18/09: NO PUEDE, CITAR A PARTIR DE OCTUBRE                       </t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
           <t>control paciente molestias testiculares persistentes oligospermia</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CITA 18/09: NO PUEDE, CITAR A PARTIR DE OCTUBRE                       </t>
-        </is>
-      </c>
+      <c r="H182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -5074,17 +6995,27 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
+          <t xml:space="preserve">Infertilidad 1º . Varicocele izquierdo                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valoración pretratamiento                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CITAR A PARTIR DE DIC., ESTA FUERA POR TRABAJO                        </t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
           <t>infertilidad 1º varicocele izquierdo</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
+      <c r="H183" t="inlineStr">
         <is>
           <t>valoracion pretratamiento</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CITAR A PARTIR DE DIC., ESTA FUERA POR TRABAJO                        </t>
         </is>
       </c>
     </row>
@@ -5104,17 +7035,27 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orquiepididimitis derecha tras prostatectomía radical. Persiste indurado y aumentado de tamaño.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO PUEDE EL 16/SEP                                                    </t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
           <t>orquiepididimitis derecha prostatectomia radical persiste indurado aumentado tamaño</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
+      <c r="H184" t="inlineStr">
         <is>
           <t>control</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NO PUEDE EL 16/SEP                                                    </t>
         </is>
       </c>
     </row>
@@ -5134,17 +7075,27 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>orquiectomia izquierda minima induracion zona post qx</t>
+          <t xml:space="preserve">ORQUIECTOMÍA IZQUIERDA, MÍNIMA INDURACIÓN, EN ZONA POST-QX.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                             </t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
+          <t xml:space="preserve">EVALUACIÓN.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                     </t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ONCO MÉDICA: GENITORUINARIO                                           </t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>orquiectomia izquierda minima induracion zona postqx</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
           <t>evaluacion</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ONCO MÉDICA: GENITORUINARIO                                           </t>
         </is>
       </c>
     </row>
@@ -5164,17 +7115,27 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
+          <t xml:space="preserve">carcinoma PRÓSTATA ESTADIO IV EN RESPUESTA A tratamiento HORMONAL. DOLOR TESTICULAR micción espontanea SUGIERE EN EPIDIDIMO DERECHO.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EPIDIDIMITIS                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                    </t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ONCO MÉDICA: GENITOURINARIO                                           </t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
           <t>carcinoma prostata estadio iv respuesta tratamiento hormonal dolor testicular miccion espontanea sugiere epididimo derecho</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
+      <c r="H186" t="inlineStr">
         <is>
           <t>epididimitis</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ONCO MÉDICA: GENITOURINARIO                                           </t>
         </is>
       </c>
     </row>
@@ -5194,17 +7155,28 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
+          <t xml:space="preserve">ORQUIECTOMÍA TESTICULAR POR TUMOR.
+LIBRE DE ENFERMEDAD.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                 </t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONTROL.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                        </t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ONCOLOGÍA MÉDICA: GENITORURINARIO                                     </t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
           <t>orquiectomia testicular tumor libre enfermedad</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
+      <c r="H187" t="inlineStr">
         <is>
           <t>control</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ONCOLOGÍA MÉDICA: GENITORURINARIO                                     </t>
         </is>
       </c>
     </row>
@@ -5224,15 +7196,25 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
+          <t xml:space="preserve">PO exéresis lesion epidídimo (benigna)                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                  </t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                               </t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PENDIENTE ECOGRAFIA DE ESCROTO                                        </t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
           <t>po exeresis lesion epididimo benigna</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PENDIENTE ECOGRAFIA DE ESCROTO                                        </t>
-        </is>
-      </c>
+      <c r="H188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -5250,17 +7232,28 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orquiectomía por tumor testicular año 2013, libre de enfermedad
+ecografía testículo contralateral                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                              </t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">control                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">onco médica: genitourinario                                           </t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
           <t>orquiectomia tumor testicular año 2013 libre enfermedad ecografia testiculo contralateral</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr">
+      <c r="H189" t="inlineStr">
         <is>
           <t>control</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">onco médica: genitourinario                                           </t>
         </is>
       </c>
     </row>

--- a/services/backend/uploads/datos_escroto.xlsx
+++ b/services/backend/uploads/datos_escroto.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlo\Documents\INGERNIERIA-INFORMATICA\4-CARRERA\MATERIAS\TFG\Proyecto_simple\services\backend\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3AC7E7E-FA89-4070-B435-09AB5EA87D12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{926F5919-0803-4EA0-A8D9-8F4369F465C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2420,10 +2420,10 @@
     <t>prioridad</t>
   </si>
   <si>
-    <t>OTHER</t>
-  </si>
-  <si>
     <t>NONE</t>
+  </si>
+  <si>
+    <t>ESCROTO</t>
   </si>
 </sst>
 </file>
@@ -2431,7 +2431,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -2464,7 +2464,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2907,13 +2907,13 @@
         <v>29</v>
       </c>
       <c r="V2" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
@@ -2975,13 +2975,13 @@
         <v>35</v>
       </c>
       <c r="V3" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
@@ -3043,13 +3043,13 @@
         <v>39</v>
       </c>
       <c r="V4" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
@@ -3111,13 +3111,13 @@
         <v>29</v>
       </c>
       <c r="V5" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W5" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X5" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
@@ -3176,13 +3176,13 @@
         <v>46</v>
       </c>
       <c r="V6" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W6" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X6" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
@@ -3244,13 +3244,13 @@
         <v>50</v>
       </c>
       <c r="V7" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W7" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X7" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
@@ -3312,13 +3312,13 @@
         <v>29</v>
       </c>
       <c r="V8" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W8" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X8" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
@@ -3380,13 +3380,13 @@
         <v>58</v>
       </c>
       <c r="V9" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W9" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X9" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
@@ -3448,13 +3448,13 @@
         <v>63</v>
       </c>
       <c r="V10" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W10" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X10" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
@@ -3516,13 +3516,13 @@
         <v>68</v>
       </c>
       <c r="V11" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W11" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X11" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
@@ -3584,13 +3584,13 @@
         <v>73</v>
       </c>
       <c r="V12" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W12" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X12" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
@@ -3652,13 +3652,13 @@
         <v>29</v>
       </c>
       <c r="V13" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W13" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X13" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
@@ -3720,13 +3720,13 @@
         <v>81</v>
       </c>
       <c r="V14" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W14" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X14" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
@@ -3788,13 +3788,13 @@
         <v>84</v>
       </c>
       <c r="V15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X15" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
@@ -3856,13 +3856,13 @@
         <v>88</v>
       </c>
       <c r="V16" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W16" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X16" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.3">
@@ -3924,13 +3924,13 @@
         <v>29</v>
       </c>
       <c r="V17" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W17" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X17" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.3">
@@ -3992,13 +3992,13 @@
         <v>35</v>
       </c>
       <c r="V18" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W18" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X18" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.3">
@@ -4060,13 +4060,13 @@
         <v>101</v>
       </c>
       <c r="V19" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W19" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X19" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.3">
@@ -4128,13 +4128,13 @@
         <v>29</v>
       </c>
       <c r="V20" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W20" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X20" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.3">
@@ -4196,13 +4196,13 @@
         <v>108</v>
       </c>
       <c r="V21" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W21" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X21" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.3">
@@ -4264,13 +4264,13 @@
         <v>112</v>
       </c>
       <c r="V22" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W22" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X22" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.3">
@@ -4332,13 +4332,13 @@
         <v>116</v>
       </c>
       <c r="V23" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W23" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X23" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.3">
@@ -4397,13 +4397,13 @@
         <v>122</v>
       </c>
       <c r="V24" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W24" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X24" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.3">
@@ -4462,13 +4462,13 @@
         <v>125</v>
       </c>
       <c r="V25" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W25" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X25" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.3">
@@ -4530,13 +4530,13 @@
         <v>81</v>
       </c>
       <c r="V26" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W26" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X26" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.3">
@@ -4598,13 +4598,13 @@
         <v>134</v>
       </c>
       <c r="V27" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W27" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X27" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.3">
@@ -4666,13 +4666,13 @@
         <v>29</v>
       </c>
       <c r="V28" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W28" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X28" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.3">
@@ -4734,13 +4734,13 @@
         <v>141</v>
       </c>
       <c r="V29" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W29" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X29" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.3">
@@ -4802,13 +4802,13 @@
         <v>29</v>
       </c>
       <c r="V30" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W30" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X30" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.3">
@@ -4870,13 +4870,13 @@
         <v>29</v>
       </c>
       <c r="V31" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W31" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X31" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.3">
@@ -4938,13 +4938,13 @@
         <v>151</v>
       </c>
       <c r="V32" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W32" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X32" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.3">
@@ -5003,13 +5003,13 @@
         <v>154</v>
       </c>
       <c r="V33" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W33" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X33" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.3">
@@ -5071,13 +5071,13 @@
         <v>159</v>
       </c>
       <c r="V34" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W34" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X34" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.3">
@@ -5139,13 +5139,13 @@
         <v>163</v>
       </c>
       <c r="V35" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W35" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X35" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.3">
@@ -5207,13 +5207,13 @@
         <v>29</v>
       </c>
       <c r="V36" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W36" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X36" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.3">
@@ -5275,13 +5275,13 @@
         <v>112</v>
       </c>
       <c r="V37" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W37" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X37" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.3">
@@ -5343,13 +5343,13 @@
         <v>174</v>
       </c>
       <c r="V38" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W38" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X38" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.3">
@@ -5411,13 +5411,13 @@
         <v>178</v>
       </c>
       <c r="V39" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W39" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X39" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.3">
@@ -5476,13 +5476,13 @@
         <v>182</v>
       </c>
       <c r="V40" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W40" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X40" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.3">
@@ -5544,13 +5544,13 @@
         <v>29</v>
       </c>
       <c r="V41" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W41" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X41" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.3">
@@ -5612,13 +5612,13 @@
         <v>191</v>
       </c>
       <c r="V42" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W42" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X42" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.3">
@@ -5680,13 +5680,13 @@
         <v>29</v>
       </c>
       <c r="V43" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W43" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X43" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.3">
@@ -5748,13 +5748,13 @@
         <v>199</v>
       </c>
       <c r="V44" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W44" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X44" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.3">
@@ -5816,13 +5816,13 @@
         <v>202</v>
       </c>
       <c r="V45" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W45" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X45" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.3">
@@ -5884,13 +5884,13 @@
         <v>207</v>
       </c>
       <c r="V46" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W46" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X46" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.3">
@@ -5952,13 +5952,13 @@
         <v>212</v>
       </c>
       <c r="V47" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W47" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X47" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.3">
@@ -6023,13 +6023,13 @@
         <v>218</v>
       </c>
       <c r="V48" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W48" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X48" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.3">
@@ -6088,13 +6088,13 @@
         <v>221</v>
       </c>
       <c r="V49" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W49" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X49" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.3">
@@ -6156,13 +6156,13 @@
         <v>226</v>
       </c>
       <c r="V50" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W50" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X50" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.3">
@@ -6224,13 +6224,13 @@
         <v>230</v>
       </c>
       <c r="V51" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W51" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X51" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.3">
@@ -6292,13 +6292,13 @@
         <v>235</v>
       </c>
       <c r="V52" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W52" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X52" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.3">
@@ -6360,13 +6360,13 @@
         <v>240</v>
       </c>
       <c r="V53" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W53" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X53" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.3">
@@ -6428,13 +6428,13 @@
         <v>246</v>
       </c>
       <c r="V54" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W54" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X54" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.3">
@@ -6493,13 +6493,13 @@
         <v>249</v>
       </c>
       <c r="V55" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W55" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X55" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="56" spans="1:24" x14ac:dyDescent="0.3">
@@ -6561,13 +6561,13 @@
         <v>207</v>
       </c>
       <c r="V56" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W56" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X56" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="57" spans="1:24" x14ac:dyDescent="0.3">
@@ -6629,13 +6629,13 @@
         <v>257</v>
       </c>
       <c r="V57" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W57" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X57" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="58" spans="1:24" x14ac:dyDescent="0.3">
@@ -6697,13 +6697,13 @@
         <v>263</v>
       </c>
       <c r="V58" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W58" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X58" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="59" spans="1:24" x14ac:dyDescent="0.3">
@@ -6765,13 +6765,13 @@
         <v>29</v>
       </c>
       <c r="V59" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W59" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X59" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.3">
@@ -6833,13 +6833,13 @@
         <v>29</v>
       </c>
       <c r="V60" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W60" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X60" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="61" spans="1:24" x14ac:dyDescent="0.3">
@@ -6901,13 +6901,13 @@
         <v>273</v>
       </c>
       <c r="V61" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W61" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X61" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="62" spans="1:24" x14ac:dyDescent="0.3">
@@ -6969,13 +6969,13 @@
         <v>278</v>
       </c>
       <c r="V62" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W62" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X62" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.3">
@@ -7037,13 +7037,13 @@
         <v>112</v>
       </c>
       <c r="V63" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W63" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X63" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.3">
@@ -7105,13 +7105,13 @@
         <v>287</v>
       </c>
       <c r="V64" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W64" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X64" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="65" spans="1:24" x14ac:dyDescent="0.3">
@@ -7173,13 +7173,13 @@
         <v>292</v>
       </c>
       <c r="V65" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W65" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X65" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="66" spans="1:24" x14ac:dyDescent="0.3">
@@ -7238,13 +7238,13 @@
         <v>294</v>
       </c>
       <c r="V66" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W66" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X66" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="67" spans="1:24" x14ac:dyDescent="0.3">
@@ -7306,13 +7306,13 @@
         <v>300</v>
       </c>
       <c r="V67" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W67" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X67" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="68" spans="1:24" x14ac:dyDescent="0.3">
@@ -7374,13 +7374,13 @@
         <v>305</v>
       </c>
       <c r="V68" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W68" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X68" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="69" spans="1:24" x14ac:dyDescent="0.3">
@@ -7442,13 +7442,13 @@
         <v>309</v>
       </c>
       <c r="V69" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W69" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X69" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="70" spans="1:24" x14ac:dyDescent="0.3">
@@ -7510,13 +7510,13 @@
         <v>29</v>
       </c>
       <c r="V70" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W70" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X70" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="71" spans="1:24" x14ac:dyDescent="0.3">
@@ -7578,13 +7578,13 @@
         <v>29</v>
       </c>
       <c r="V71" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W71" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X71" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="72" spans="1:24" x14ac:dyDescent="0.3">
@@ -7646,13 +7646,13 @@
         <v>29</v>
       </c>
       <c r="V72" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W72" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X72" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="73" spans="1:24" x14ac:dyDescent="0.3">
@@ -7714,13 +7714,13 @@
         <v>323</v>
       </c>
       <c r="V73" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W73" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X73" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="74" spans="1:24" x14ac:dyDescent="0.3">
@@ -7782,13 +7782,13 @@
         <v>29</v>
       </c>
       <c r="V74" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W74" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X74" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="75" spans="1:24" x14ac:dyDescent="0.3">
@@ -7850,13 +7850,13 @@
         <v>29</v>
       </c>
       <c r="V75" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W75" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X75" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="76" spans="1:24" x14ac:dyDescent="0.3">
@@ -7918,13 +7918,13 @@
         <v>29</v>
       </c>
       <c r="V76" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W76" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X76" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="77" spans="1:24" x14ac:dyDescent="0.3">
@@ -7986,13 +7986,13 @@
         <v>336</v>
       </c>
       <c r="V77" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W77" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X77" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="78" spans="1:24" x14ac:dyDescent="0.3">
@@ -8054,13 +8054,13 @@
         <v>340</v>
       </c>
       <c r="V78" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W78" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X78" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="79" spans="1:24" x14ac:dyDescent="0.3">
@@ -8119,13 +8119,13 @@
         <v>342</v>
       </c>
       <c r="V79" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W79" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X79" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="80" spans="1:24" x14ac:dyDescent="0.3">
@@ -8187,13 +8187,13 @@
         <v>29</v>
       </c>
       <c r="V80" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W80" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X80" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="81" spans="1:24" x14ac:dyDescent="0.3">
@@ -8255,13 +8255,13 @@
         <v>348</v>
       </c>
       <c r="V81" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W81" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X81" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="82" spans="1:24" x14ac:dyDescent="0.3">
@@ -8323,13 +8323,13 @@
         <v>352</v>
       </c>
       <c r="V82" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W82" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X82" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="83" spans="1:24" x14ac:dyDescent="0.3">
@@ -8388,13 +8388,13 @@
         <v>355</v>
       </c>
       <c r="V83" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W83" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X83" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="84" spans="1:24" x14ac:dyDescent="0.3">
@@ -8456,13 +8456,13 @@
         <v>360</v>
       </c>
       <c r="V84" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W84" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X84" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="85" spans="1:24" x14ac:dyDescent="0.3">
@@ -8521,13 +8521,13 @@
         <v>362</v>
       </c>
       <c r="V85" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W85" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X85" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="86" spans="1:24" x14ac:dyDescent="0.3">
@@ -8589,13 +8589,13 @@
         <v>367</v>
       </c>
       <c r="V86" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W86" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X86" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="87" spans="1:24" x14ac:dyDescent="0.3">
@@ -8657,13 +8657,13 @@
         <v>372</v>
       </c>
       <c r="V87" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W87" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X87" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="88" spans="1:24" x14ac:dyDescent="0.3">
@@ -8725,13 +8725,13 @@
         <v>377</v>
       </c>
       <c r="V88" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W88" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X88" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="89" spans="1:24" x14ac:dyDescent="0.3">
@@ -8793,13 +8793,13 @@
         <v>158</v>
       </c>
       <c r="V89" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W89" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X89" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="90" spans="1:24" x14ac:dyDescent="0.3">
@@ -8861,13 +8861,13 @@
         <v>386</v>
       </c>
       <c r="V90" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W90" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X90" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="91" spans="1:24" x14ac:dyDescent="0.3">
@@ -8929,13 +8929,13 @@
         <v>391</v>
       </c>
       <c r="V91" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W91" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X91" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="92" spans="1:24" x14ac:dyDescent="0.3">
@@ -8997,13 +8997,13 @@
         <v>395</v>
       </c>
       <c r="V92" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W92" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X92" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="93" spans="1:24" x14ac:dyDescent="0.3">
@@ -9065,13 +9065,13 @@
         <v>399</v>
       </c>
       <c r="V93" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W93" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X93" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="94" spans="1:24" x14ac:dyDescent="0.3">
@@ -9133,13 +9133,13 @@
         <v>404</v>
       </c>
       <c r="V94" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W94" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X94" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="95" spans="1:24" x14ac:dyDescent="0.3">
@@ -9201,13 +9201,13 @@
         <v>409</v>
       </c>
       <c r="V95" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W95" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X95" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="96" spans="1:24" x14ac:dyDescent="0.3">
@@ -9269,13 +9269,13 @@
         <v>414</v>
       </c>
       <c r="V96" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W96" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X96" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="97" spans="1:24" x14ac:dyDescent="0.3">
@@ -9337,13 +9337,13 @@
         <v>419</v>
       </c>
       <c r="V97" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W97" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X97" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="98" spans="1:24" x14ac:dyDescent="0.3">
@@ -9405,13 +9405,13 @@
         <v>424</v>
       </c>
       <c r="V98" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W98" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X98" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="99" spans="1:24" x14ac:dyDescent="0.3">
@@ -9473,13 +9473,13 @@
         <v>29</v>
       </c>
       <c r="V99" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W99" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X99" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="100" spans="1:24" x14ac:dyDescent="0.3">
@@ -9541,13 +9541,13 @@
         <v>207</v>
       </c>
       <c r="V100" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W100" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X100" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="101" spans="1:24" x14ac:dyDescent="0.3">
@@ -9609,13 +9609,13 @@
         <v>433</v>
       </c>
       <c r="V101" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W101" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X101" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="102" spans="1:24" x14ac:dyDescent="0.3">
@@ -9677,13 +9677,13 @@
         <v>438</v>
       </c>
       <c r="V102" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W102" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X102" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="103" spans="1:24" x14ac:dyDescent="0.3">
@@ -9745,13 +9745,13 @@
         <v>444</v>
       </c>
       <c r="V103" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W103" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X103" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="104" spans="1:24" x14ac:dyDescent="0.3">
@@ -9810,13 +9810,13 @@
         <v>447</v>
       </c>
       <c r="V104" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W104" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X104" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="105" spans="1:24" x14ac:dyDescent="0.3">
@@ -9878,13 +9878,13 @@
         <v>29</v>
       </c>
       <c r="V105" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W105" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X105" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="106" spans="1:24" x14ac:dyDescent="0.3">
@@ -9946,13 +9946,13 @@
         <v>455</v>
       </c>
       <c r="V106" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W106" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X106" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="107" spans="1:24" x14ac:dyDescent="0.3">
@@ -10014,13 +10014,13 @@
         <v>29</v>
       </c>
       <c r="V107" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W107" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X107" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="108" spans="1:24" x14ac:dyDescent="0.3">
@@ -10082,13 +10082,13 @@
         <v>462</v>
       </c>
       <c r="V108" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W108" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X108" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="109" spans="1:24" x14ac:dyDescent="0.3">
@@ -10150,13 +10150,13 @@
         <v>466</v>
       </c>
       <c r="V109" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W109" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X109" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="110" spans="1:24" x14ac:dyDescent="0.3">
@@ -10218,13 +10218,13 @@
         <v>470</v>
       </c>
       <c r="V110" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W110" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X110" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="111" spans="1:24" x14ac:dyDescent="0.3">
@@ -10283,13 +10283,13 @@
         <v>472</v>
       </c>
       <c r="V111" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W111" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X111" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="112" spans="1:24" x14ac:dyDescent="0.3">
@@ -10351,13 +10351,13 @@
         <v>112</v>
       </c>
       <c r="V112" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W112" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X112" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="113" spans="1:24" x14ac:dyDescent="0.3">
@@ -10419,13 +10419,13 @@
         <v>426</v>
       </c>
       <c r="V113" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W113" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X113" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="114" spans="1:24" x14ac:dyDescent="0.3">
@@ -10484,13 +10484,13 @@
         <v>482</v>
       </c>
       <c r="V114" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W114" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X114" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="115" spans="1:24" x14ac:dyDescent="0.3">
@@ -10552,13 +10552,13 @@
         <v>487</v>
       </c>
       <c r="V115" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W115" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X115" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="116" spans="1:24" x14ac:dyDescent="0.3">
@@ -10620,13 +10620,13 @@
         <v>492</v>
       </c>
       <c r="V116" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W116" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X116" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="117" spans="1:24" x14ac:dyDescent="0.3">
@@ -10688,13 +10688,13 @@
         <v>29</v>
       </c>
       <c r="V117" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W117" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X117" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="118" spans="1:24" x14ac:dyDescent="0.3">
@@ -10756,13 +10756,13 @@
         <v>29</v>
       </c>
       <c r="V118" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W118" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X118" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="119" spans="1:24" x14ac:dyDescent="0.3">
@@ -10821,13 +10821,13 @@
         <v>500</v>
       </c>
       <c r="V119" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W119" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X119" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="120" spans="1:24" x14ac:dyDescent="0.3">
@@ -10889,13 +10889,13 @@
         <v>318</v>
       </c>
       <c r="V120" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W120" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X120" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="121" spans="1:24" x14ac:dyDescent="0.3">
@@ -10954,13 +10954,13 @@
         <v>509</v>
       </c>
       <c r="V121" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W121" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X121" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="122" spans="1:24" x14ac:dyDescent="0.3">
@@ -11022,13 +11022,13 @@
         <v>53</v>
       </c>
       <c r="V122" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W122" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X122" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="123" spans="1:24" x14ac:dyDescent="0.3">
@@ -11090,13 +11090,13 @@
         <v>318</v>
       </c>
       <c r="V123" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W123" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X123" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="124" spans="1:24" x14ac:dyDescent="0.3">
@@ -11158,13 +11158,13 @@
         <v>462</v>
       </c>
       <c r="V124" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W124" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X124" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="125" spans="1:24" x14ac:dyDescent="0.3">
@@ -11226,13 +11226,13 @@
         <v>462</v>
       </c>
       <c r="V125" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W125" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X125" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="126" spans="1:24" x14ac:dyDescent="0.3">
@@ -11294,13 +11294,13 @@
         <v>318</v>
       </c>
       <c r="V126" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W126" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X126" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="127" spans="1:24" x14ac:dyDescent="0.3">
@@ -11362,13 +11362,13 @@
         <v>527</v>
       </c>
       <c r="V127" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W127" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X127" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="128" spans="1:24" x14ac:dyDescent="0.3">
@@ -11430,13 +11430,13 @@
         <v>531</v>
       </c>
       <c r="V128" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W128" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X128" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="129" spans="1:24" x14ac:dyDescent="0.3">
@@ -11498,13 +11498,13 @@
         <v>535</v>
       </c>
       <c r="V129" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W129" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X129" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="130" spans="1:24" x14ac:dyDescent="0.3">
@@ -11566,13 +11566,13 @@
         <v>541</v>
       </c>
       <c r="V130" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W130" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X130" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="131" spans="1:24" x14ac:dyDescent="0.3">
@@ -11631,13 +11631,13 @@
         <v>543</v>
       </c>
       <c r="V131" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W131" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X131" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="132" spans="1:24" x14ac:dyDescent="0.3">
@@ -11699,13 +11699,13 @@
         <v>318</v>
       </c>
       <c r="V132" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W132" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X132" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.3">
@@ -11767,13 +11767,13 @@
         <v>552</v>
       </c>
       <c r="V133" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W133" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X133" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="134" spans="1:24" x14ac:dyDescent="0.3">
@@ -11835,13 +11835,13 @@
         <v>29</v>
       </c>
       <c r="V134" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W134" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X134" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="135" spans="1:24" x14ac:dyDescent="0.3">
@@ -11903,13 +11903,13 @@
         <v>318</v>
       </c>
       <c r="V135" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W135" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X135" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="136" spans="1:24" x14ac:dyDescent="0.3">
@@ -11974,13 +11974,13 @@
         <v>563</v>
       </c>
       <c r="V136" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W136" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X136" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="137" spans="1:24" x14ac:dyDescent="0.3">
@@ -12039,13 +12039,13 @@
         <v>566</v>
       </c>
       <c r="V137" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W137" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X137" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="138" spans="1:24" x14ac:dyDescent="0.3">
@@ -12107,13 +12107,13 @@
         <v>570</v>
       </c>
       <c r="V138" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W138" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X138" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="139" spans="1:24" x14ac:dyDescent="0.3">
@@ -12175,13 +12175,13 @@
         <v>574</v>
       </c>
       <c r="V139" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W139" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X139" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="140" spans="1:24" x14ac:dyDescent="0.3">
@@ -12246,13 +12246,13 @@
         <v>578</v>
       </c>
       <c r="V140" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W140" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X140" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="141" spans="1:24" x14ac:dyDescent="0.3">
@@ -12314,13 +12314,13 @@
         <v>583</v>
       </c>
       <c r="V141" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W141" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X141" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="142" spans="1:24" x14ac:dyDescent="0.3">
@@ -12382,13 +12382,13 @@
         <v>492</v>
       </c>
       <c r="V142" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W142" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X142" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="143" spans="1:24" x14ac:dyDescent="0.3">
@@ -12450,13 +12450,13 @@
         <v>588</v>
       </c>
       <c r="V143" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W143" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X143" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="144" spans="1:24" x14ac:dyDescent="0.3">
@@ -12518,13 +12518,13 @@
         <v>593</v>
       </c>
       <c r="V144" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W144" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X144" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="145" spans="1:24" x14ac:dyDescent="0.3">
@@ -12583,13 +12583,13 @@
         <v>596</v>
       </c>
       <c r="V145" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W145" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X145" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="146" spans="1:24" x14ac:dyDescent="0.3">
@@ -12651,13 +12651,13 @@
         <v>600</v>
       </c>
       <c r="V146" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W146" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X146" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="147" spans="1:24" x14ac:dyDescent="0.3">
@@ -12719,13 +12719,13 @@
         <v>605</v>
       </c>
       <c r="V147" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W147" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X147" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="148" spans="1:24" x14ac:dyDescent="0.3">
@@ -12787,13 +12787,13 @@
         <v>607</v>
       </c>
       <c r="V148" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W148" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X148" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="149" spans="1:24" x14ac:dyDescent="0.3">
@@ -12855,13 +12855,13 @@
         <v>367</v>
       </c>
       <c r="V149" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W149" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X149" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="150" spans="1:24" x14ac:dyDescent="0.3">
@@ -12923,13 +12923,13 @@
         <v>614</v>
       </c>
       <c r="V150" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W150" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X150" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="151" spans="1:24" x14ac:dyDescent="0.3">
@@ -12991,13 +12991,13 @@
         <v>574</v>
       </c>
       <c r="V151" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W151" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X151" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="152" spans="1:24" x14ac:dyDescent="0.3">
@@ -13059,13 +13059,13 @@
         <v>621</v>
       </c>
       <c r="V152" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W152" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X152" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="153" spans="1:24" x14ac:dyDescent="0.3">
@@ -13127,13 +13127,13 @@
         <v>624</v>
       </c>
       <c r="V153" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W153" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X153" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="154" spans="1:24" x14ac:dyDescent="0.3">
@@ -13195,13 +13195,13 @@
         <v>629</v>
       </c>
       <c r="V154" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W154" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X154" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="155" spans="1:24" x14ac:dyDescent="0.3">
@@ -13263,13 +13263,13 @@
         <v>29</v>
       </c>
       <c r="V155" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W155" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X155" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="156" spans="1:24" x14ac:dyDescent="0.3">
@@ -13331,13 +13331,13 @@
         <v>638</v>
       </c>
       <c r="V156" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W156" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X156" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="157" spans="1:24" x14ac:dyDescent="0.3">
@@ -13399,13 +13399,13 @@
         <v>642</v>
       </c>
       <c r="V157" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W157" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X157" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="158" spans="1:24" x14ac:dyDescent="0.3">
@@ -13467,13 +13467,13 @@
         <v>647</v>
       </c>
       <c r="V158" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W158" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X158" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="159" spans="1:24" x14ac:dyDescent="0.3">
@@ -13535,13 +13535,13 @@
         <v>318</v>
       </c>
       <c r="V159" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W159" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X159" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="160" spans="1:24" x14ac:dyDescent="0.3">
@@ -13603,13 +13603,13 @@
         <v>654</v>
       </c>
       <c r="V160" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W160" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X160" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="161" spans="1:24" x14ac:dyDescent="0.3">
@@ -13671,13 +13671,13 @@
         <v>657</v>
       </c>
       <c r="V161" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W161" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X161" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="162" spans="1:24" x14ac:dyDescent="0.3">
@@ -13739,13 +13739,13 @@
         <v>29</v>
       </c>
       <c r="V162" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W162" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X162" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="163" spans="1:24" x14ac:dyDescent="0.3">
@@ -13807,13 +13807,13 @@
         <v>665</v>
       </c>
       <c r="V163" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W163" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X163" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="164" spans="1:24" x14ac:dyDescent="0.3">
@@ -13875,13 +13875,13 @@
         <v>669</v>
       </c>
       <c r="V164" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W164" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X164" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="165" spans="1:24" x14ac:dyDescent="0.3">
@@ -13943,13 +13943,13 @@
         <v>672</v>
       </c>
       <c r="V165" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W165" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X165" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="166" spans="1:24" x14ac:dyDescent="0.3">
@@ -14011,13 +14011,13 @@
         <v>676</v>
       </c>
       <c r="V166" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W166" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X166" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="167" spans="1:24" x14ac:dyDescent="0.3">
@@ -14082,13 +14082,13 @@
         <v>680</v>
       </c>
       <c r="V167" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W167" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X167" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="168" spans="1:24" x14ac:dyDescent="0.3">
@@ -14147,13 +14147,13 @@
         <v>682</v>
       </c>
       <c r="V168" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W168" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X168" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="169" spans="1:24" x14ac:dyDescent="0.3">
@@ -14212,13 +14212,13 @@
         <v>684</v>
       </c>
       <c r="V169" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W169" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X169" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="170" spans="1:24" x14ac:dyDescent="0.3">
@@ -14277,13 +14277,13 @@
         <v>686</v>
       </c>
       <c r="V170" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W170" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X170" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="171" spans="1:24" x14ac:dyDescent="0.3">
@@ -14342,13 +14342,13 @@
         <v>688</v>
       </c>
       <c r="V171" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W171" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X171" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="172" spans="1:24" x14ac:dyDescent="0.3">
@@ -14410,13 +14410,13 @@
         <v>29</v>
       </c>
       <c r="V172" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W172" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X172" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="173" spans="1:24" x14ac:dyDescent="0.3">
@@ -14478,13 +14478,13 @@
         <v>578</v>
       </c>
       <c r="V173" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W173" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X173" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="174" spans="1:24" x14ac:dyDescent="0.3">
@@ -14546,13 +14546,13 @@
         <v>694</v>
       </c>
       <c r="V174" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W174" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X174" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="175" spans="1:24" x14ac:dyDescent="0.3">
@@ -14614,13 +14614,13 @@
         <v>697</v>
       </c>
       <c r="V175" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W175" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X175" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="176" spans="1:24" x14ac:dyDescent="0.3">
@@ -14679,13 +14679,13 @@
         <v>700</v>
       </c>
       <c r="V176" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W176" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X176" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="177" spans="1:24" x14ac:dyDescent="0.3">
@@ -14747,13 +14747,13 @@
         <v>703</v>
       </c>
       <c r="V177" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W177" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X177" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="178" spans="1:24" x14ac:dyDescent="0.3">
@@ -14815,13 +14815,13 @@
         <v>707</v>
       </c>
       <c r="V178" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W178" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X178" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="179" spans="1:24" x14ac:dyDescent="0.3">
@@ -14883,13 +14883,13 @@
         <v>712</v>
       </c>
       <c r="V179" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W179" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X179" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="180" spans="1:24" x14ac:dyDescent="0.3">
@@ -14954,13 +14954,13 @@
         <v>717</v>
       </c>
       <c r="V180" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W180" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X180" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="181" spans="1:24" x14ac:dyDescent="0.3">
@@ -15025,13 +15025,13 @@
         <v>723</v>
       </c>
       <c r="V181" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W181" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X181" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="182" spans="1:24" x14ac:dyDescent="0.3">
@@ -15093,13 +15093,13 @@
         <v>727</v>
       </c>
       <c r="V182" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W182" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X182" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="183" spans="1:24" x14ac:dyDescent="0.3">
@@ -15164,13 +15164,13 @@
         <v>733</v>
       </c>
       <c r="V183" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W183" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X183" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="184" spans="1:24" x14ac:dyDescent="0.3">
@@ -15235,13 +15235,13 @@
         <v>29</v>
       </c>
       <c r="V184" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W184" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X184" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="185" spans="1:24" x14ac:dyDescent="0.3">
@@ -15306,13 +15306,13 @@
         <v>743</v>
       </c>
       <c r="V185" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W185" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X185" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="186" spans="1:24" x14ac:dyDescent="0.3">
@@ -15377,13 +15377,13 @@
         <v>748</v>
       </c>
       <c r="V186" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W186" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X186" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="187" spans="1:24" x14ac:dyDescent="0.3">
@@ -15451,13 +15451,13 @@
         <v>29</v>
       </c>
       <c r="V187" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W187" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X187" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="188" spans="1:24" x14ac:dyDescent="0.3">
@@ -15519,13 +15519,13 @@
         <v>757</v>
       </c>
       <c r="V188" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W188" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X188" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="189" spans="1:24" x14ac:dyDescent="0.3">
@@ -15590,13 +15590,13 @@
         <v>29</v>
       </c>
       <c r="V189" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W189" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="X189" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
   </sheetData>
